--- a/Data/日间手术总结报表.xlsx
+++ b/Data/日间手术总结报表.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,10 +390,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>817</v>
+      <c r="B3">
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -403,7 +411,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:32">
@@ -503,99 +511,197 @@
     </row>
     <row r="2" spans="1:32">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>14</v>
-      </c>
-      <c r="D2">
-        <v>17</v>
-      </c>
-      <c r="E2">
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>24</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>32</v>
+      </c>
+      <c r="H3">
+        <v>29</v>
+      </c>
+      <c r="I3">
+        <v>29</v>
+      </c>
+      <c r="J3">
+        <v>37</v>
+      </c>
+      <c r="K3">
         <v>25</v>
       </c>
-      <c r="F2">
+      <c r="L3">
+        <v>43</v>
+      </c>
+      <c r="M3">
+        <v>38</v>
+      </c>
+      <c r="N3">
+        <v>36</v>
+      </c>
+      <c r="O3">
+        <v>30</v>
+      </c>
+      <c r="P3">
+        <v>31</v>
+      </c>
+      <c r="Q3">
+        <v>27</v>
+      </c>
+      <c r="R3">
+        <v>26</v>
+      </c>
+      <c r="S3">
+        <v>31</v>
+      </c>
+      <c r="T3">
+        <v>34</v>
+      </c>
+      <c r="U3">
+        <v>40</v>
+      </c>
+      <c r="V3">
+        <v>32</v>
+      </c>
+      <c r="W3">
+        <v>33</v>
+      </c>
+      <c r="X3">
+        <v>24</v>
+      </c>
+      <c r="Y3">
+        <v>45</v>
+      </c>
+      <c r="Z3">
+        <v>29</v>
+      </c>
+      <c r="AA3">
+        <v>31</v>
+      </c>
+      <c r="AB3">
+        <v>24</v>
+      </c>
+      <c r="AC3">
+        <v>26</v>
+      </c>
+      <c r="AD3">
+        <v>33</v>
+      </c>
+      <c r="AE3">
         <v>20</v>
       </c>
-      <c r="G2">
-        <v>26</v>
-      </c>
-      <c r="H2">
-        <v>29</v>
-      </c>
-      <c r="I2">
-        <v>29</v>
-      </c>
-      <c r="J2">
-        <v>25</v>
-      </c>
-      <c r="K2">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>38</v>
-      </c>
-      <c r="M2">
-        <v>36</v>
-      </c>
-      <c r="N2">
-        <v>32</v>
-      </c>
-      <c r="O2">
-        <v>30</v>
-      </c>
-      <c r="P2">
-        <v>31</v>
-      </c>
-      <c r="Q2">
-        <v>22</v>
-      </c>
-      <c r="R2">
-        <v>21</v>
-      </c>
-      <c r="S2">
-        <v>28</v>
-      </c>
-      <c r="T2">
-        <v>31</v>
-      </c>
-      <c r="U2">
-        <v>37</v>
-      </c>
-      <c r="V2">
-        <v>30</v>
-      </c>
-      <c r="W2">
-        <v>32</v>
-      </c>
-      <c r="X2">
-        <v>21</v>
-      </c>
-      <c r="Y2">
-        <v>34</v>
-      </c>
-      <c r="Z2">
-        <v>28</v>
-      </c>
-      <c r="AA2">
-        <v>31</v>
-      </c>
-      <c r="AB2">
-        <v>24</v>
-      </c>
-      <c r="AC2">
-        <v>26</v>
-      </c>
-      <c r="AD2">
-        <v>33</v>
-      </c>
-      <c r="AE2">
-        <v>20</v>
-      </c>
-      <c r="AF2">
+      <c r="AF3">
         <v>13</v>
       </c>
     </row>
@@ -606,7 +712,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -634,28 +740,54 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>163</v>
-      </c>
-      <c r="C2">
-        <v>157</v>
-      </c>
-      <c r="D2">
-        <v>157</v>
-      </c>
-      <c r="E2">
-        <v>118</v>
-      </c>
-      <c r="F2">
-        <v>139</v>
-      </c>
-      <c r="G2">
-        <v>41</v>
-      </c>
-      <c r="H2">
-        <v>42</v>
+      <c r="B3">
+        <v>189</v>
+      </c>
+      <c r="C3">
+        <v>183</v>
+      </c>
+      <c r="D3">
+        <v>171</v>
+      </c>
+      <c r="E3">
+        <v>125</v>
+      </c>
+      <c r="F3">
+        <v>152</v>
+      </c>
+      <c r="G3">
+        <v>43</v>
+      </c>
+      <c r="H3">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +797,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -975,6 +1107,32 @@
       </c>
       <c r="H12">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>26</v>
+      </c>
+      <c r="C13">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1081,6 +1239,14 @@
       </c>
       <c r="B12">
         <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1090,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1426,7 +1592,39 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>23</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>49</v>
+      </c>
+      <c r="B43">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>50</v>
+      </c>
+      <c r="B44">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>51</v>
+      </c>
+      <c r="B45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>52</v>
+      </c>
+      <c r="B46">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1452,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>163</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1460,7 +1658,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>157</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1468,7 +1666,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1476,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1484,7 +1682,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1492,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1500,7 +1698,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1724,7 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>817</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>
@@ -1552,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1632,7 +1830,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1883,7 @@
         <v>2024</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>31</v>
@@ -1715,7 +1913,7 @@
         <v>128</v>
       </c>
       <c r="L2">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1725,10 +1923,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1">
         <v>1</v>
       </c>
@@ -1762,43 +1960,90 @@
       <c r="L1">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>41</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>76</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>83</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>86</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>105</v>
       </c>
-      <c r="I2">
+      <c r="I3">
         <v>99</v>
       </c>
-      <c r="J2">
+      <c r="J3">
         <v>105</v>
       </c>
-      <c r="K2">
+      <c r="K3">
         <v>95</v>
       </c>
-      <c r="L2">
+      <c r="L3">
         <v>125</v>
+      </c>
+      <c r="M3">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1808,10 +2053,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:46">
       <c r="B1">
         <v>4</v>
       </c>
@@ -1935,133 +2180,297 @@
       <c r="AP1">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:42">
+      <c r="AQ1">
+        <v>49</v>
+      </c>
+      <c r="AR1">
+        <v>50</v>
+      </c>
+      <c r="AS1">
+        <v>51</v>
+      </c>
+      <c r="AT1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46">
       <c r="A2">
+        <v>2023</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:46">
+      <c r="A3">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>7</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>15</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>13</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>10</v>
       </c>
-      <c r="I2">
+      <c r="I3">
         <v>13</v>
       </c>
-      <c r="J2">
+      <c r="J3">
         <v>23</v>
       </c>
-      <c r="K2">
+      <c r="K3">
         <v>26</v>
       </c>
-      <c r="L2">
+      <c r="L3">
         <v>5</v>
       </c>
-      <c r="M2">
+      <c r="M3">
         <v>23</v>
       </c>
-      <c r="N2">
+      <c r="N3">
         <v>23</v>
       </c>
-      <c r="O2">
+      <c r="O3">
         <v>19</v>
       </c>
-      <c r="P2">
+      <c r="P3">
         <v>18</v>
       </c>
-      <c r="Q2">
+      <c r="Q3">
         <v>20</v>
       </c>
-      <c r="R2">
+      <c r="R3">
         <v>23</v>
       </c>
-      <c r="S2">
+      <c r="S3">
         <v>21</v>
       </c>
-      <c r="T2">
+      <c r="T3">
         <v>21</v>
       </c>
-      <c r="U2">
+      <c r="U3">
         <v>22</v>
       </c>
-      <c r="V2">
+      <c r="V3">
         <v>33</v>
       </c>
-      <c r="W2">
+      <c r="W3">
         <v>22</v>
       </c>
-      <c r="X2">
+      <c r="X3">
         <v>20</v>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <v>14</v>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <v>25</v>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <v>21</v>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <v>26</v>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <v>22</v>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <v>24</v>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <v>24</v>
       </c>
-      <c r="AF2">
+      <c r="AF3">
         <v>24</v>
       </c>
-      <c r="AG2">
+      <c r="AG3">
         <v>26</v>
       </c>
-      <c r="AH2">
+      <c r="AH3">
         <v>8</v>
       </c>
-      <c r="AI2">
+      <c r="AI3">
         <v>23</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ3">
         <v>22</v>
       </c>
-      <c r="AK2">
+      <c r="AK3">
         <v>29</v>
       </c>
-      <c r="AL2">
+      <c r="AL3">
         <v>23</v>
       </c>
-      <c r="AM2">
+      <c r="AM3">
         <v>33</v>
       </c>
-      <c r="AN2">
+      <c r="AN3">
         <v>34</v>
       </c>
-      <c r="AO2">
+      <c r="AO3">
         <v>31</v>
       </c>
-      <c r="AP2">
-        <v>23</v>
+      <c r="AP3">
+        <v>24</v>
+      </c>
+      <c r="AQ3">
+        <v>26</v>
+      </c>
+      <c r="AR3">
+        <v>26</v>
+      </c>
+      <c r="AS3">
+        <v>22</v>
+      </c>
+      <c r="AT3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
